--- a/Exported/comparison/au4_5_7_summary.xlsx
+++ b/Exported/comparison/au4_5_7_summary.xlsx
@@ -580,22 +580,22 @@
         <v>8262</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1878854998789639</v>
+        <v>0.1865165819414185</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3031527352408676</v>
+        <v>0.2975984551081935</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07258533042846768</v>
+        <v>0.08571411280561608</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1784120657099816</v>
+        <v>0.1953530280297643</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7448934882595013</v>
+        <v>0.727840716533527</v>
       </c>
       <c r="H6" t="n">
-        <v>0.669200512026051</v>
+        <v>0.657172588784206</v>
       </c>
     </row>
     <row r="7">
@@ -608,22 +608,22 @@
         <v>10858</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1665693497881746</v>
+        <v>0.1675382206667894</v>
       </c>
       <c r="D7" t="n">
-        <v>0.279713584658879</v>
+        <v>0.2764713869485832</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1538671946951556</v>
+        <v>0.08202523484988027</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2685082256931345</v>
+        <v>0.1928179375239963</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6560747835697182</v>
+        <v>0.6650138146988396</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6430755224644035</v>
+        <v>0.6506230601453559</v>
       </c>
     </row>
     <row r="8">
@@ -633,25 +633,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6770</v>
+        <v>6769</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04262629246676514</v>
+        <v>0.04919042694637318</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1449750767012066</v>
+        <v>0.1594195493707778</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09275480059084196</v>
+        <v>0.08571133106810461</v>
       </c>
       <c r="F8" t="n">
-        <v>0.21378367647997</v>
+        <v>0.1998657202669855</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6963456425406204</v>
+        <v>0.6924449697148766</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5800348168107909</v>
+        <v>0.5683355997842772</v>
       </c>
     </row>
     <row r="9">
@@ -664,22 +664,22 @@
         <v>13789</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4209456813401987</v>
+        <v>0.4200311842773224</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5402809461272328</v>
+        <v>0.5446277094808396</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1131104503589818</v>
+        <v>0.07343824787874394</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2057282896313356</v>
+        <v>0.1549040459959564</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6267800420625136</v>
+        <v>0.6106055551526579</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3965829198540421</v>
+        <v>0.3969293075925271</v>
       </c>
     </row>
     <row r="10">
@@ -692,22 +692,22 @@
         <v>6325</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9730735177865614</v>
+        <v>0.9702387351778656</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5479446459665094</v>
+        <v>0.5363945304243087</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06753675889328063</v>
+        <v>0.09483003952569169</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2008745988809394</v>
+        <v>0.2437389749343307</v>
       </c>
       <c r="G10" t="n">
-        <v>1.360105928853755</v>
+        <v>1.367805533596838</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8321637613950761</v>
+        <v>0.8353014905650249</v>
       </c>
     </row>
     <row r="11">
@@ -717,25 +717,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10534</v>
+        <v>10532</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7750408202012532</v>
+        <v>0.7674306874287884</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4940303782797002</v>
+        <v>0.4811607087178721</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09687298272261249</v>
+        <v>0.1317071781238131</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2731337242724453</v>
+        <v>0.3259483442744441</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9542139737991265</v>
+        <v>0.9513140903911887</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4452251226363473</v>
+        <v>0.4446060324272965</v>
       </c>
     </row>
     <row r="12">
@@ -748,22 +748,22 @@
         <v>2854</v>
       </c>
       <c r="C12" t="n">
-        <v>1.071433076384022</v>
+        <v>1.076166783461808</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4981338602203914</v>
+        <v>0.486587747159358</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08415907498248072</v>
+        <v>0.09069025928521372</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2602488306045587</v>
+        <v>0.2458467774678168</v>
       </c>
       <c r="G12" t="n">
-        <v>2.207536790469516</v>
+        <v>2.203006306937631</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7213509115697456</v>
+        <v>0.6821558694125696</v>
       </c>
     </row>
     <row r="13">
@@ -776,22 +776,22 @@
         <v>6860</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2399708454810496</v>
+        <v>0.2449970845481049</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3443276618758936</v>
+        <v>0.3398650495759565</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05833673469387754</v>
+        <v>0.09591399416909621</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2049711404386519</v>
+        <v>0.2497800079617984</v>
       </c>
       <c r="G13" t="n">
-        <v>1.274637026239067</v>
+        <v>1.258801749271137</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6053180025971173</v>
+        <v>0.5965636335585103</v>
       </c>
     </row>
     <row r="14">
@@ -804,22 +804,22 @@
         <v>7237</v>
       </c>
       <c r="C14" t="n">
-        <v>1.241887522454056</v>
+        <v>1.221655382064391</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4176482991404538</v>
+        <v>0.4034544670494482</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04975542351803234</v>
+        <v>0.05435401409423794</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1381075537144267</v>
+        <v>0.1363077766676736</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6503026115793837</v>
+        <v>0.6412297913500069</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3842173880533846</v>
+        <v>0.3803547947387191</v>
       </c>
     </row>
     <row r="15">
@@ -829,25 +829,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10169</v>
+        <v>10167</v>
       </c>
       <c r="C15" t="n">
-        <v>1.667315370242895</v>
+        <v>1.654733943149405</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4218331950592994</v>
+        <v>0.4329955111331317</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03685908152227358</v>
+        <v>0.08649355758827579</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1300640158396914</v>
+        <v>0.2121552869036424</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1409597797226866</v>
+        <v>0.1341280613750369</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1979626343970448</v>
+        <v>0.1948369691483881</v>
       </c>
     </row>
   </sheetData>

--- a/Exported/comparison/au4_5_7_summary.xlsx
+++ b/Exported/comparison/au4_5_7_summary.xlsx
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8262</v>
+        <v>14815</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1865165819414185</v>
+        <v>0.1723057711778603</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2975984551081935</v>
+        <v>0.31612616519231</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08571411280561608</v>
+        <v>0.09227472156598042</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1953530280297643</v>
+        <v>0.2154656781887409</v>
       </c>
       <c r="G6" t="n">
-        <v>0.727840716533527</v>
+        <v>0.6251076611542357</v>
       </c>
       <c r="H6" t="n">
-        <v>0.657172588784206</v>
+        <v>0.5616866562202797</v>
       </c>
     </row>
     <row r="7">
@@ -605,25 +605,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10858</v>
+        <v>13869</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1675382206667894</v>
+        <v>0.1689566659456341</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2764713869485832</v>
+        <v>0.2710624710414783</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08202523484988027</v>
+        <v>0.08343355685341408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1928179375239963</v>
+        <v>0.1944890976052319</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6650138146988396</v>
+        <v>0.6031004398298363</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6506230601453559</v>
+        <v>0.6211053259024486</v>
       </c>
     </row>
     <row r="8">
@@ -633,25 +633,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6769</v>
+        <v>17640</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04919042694637318</v>
+        <v>0.04857993197278912</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1594195493707778</v>
+        <v>0.1507506638295277</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08571133106810461</v>
+        <v>0.08175113378684806</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1998657202669855</v>
+        <v>0.1990794631781393</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6924449697148766</v>
+        <v>0.4088412698412699</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5683355997842772</v>
+        <v>0.4651144159199622</v>
       </c>
     </row>
     <row r="9">
@@ -661,25 +661,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13789</v>
+        <v>18250</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4200311842773224</v>
+        <v>0.3335052054794521</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5446277094808396</v>
+        <v>0.4466792416218947</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07343824787874394</v>
+        <v>0.0753731506849315</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1549040459959564</v>
+        <v>0.1628072926000114</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6106055551526579</v>
+        <v>0.5516920547945207</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3969293075925271</v>
+        <v>0.4112148954605951</v>
       </c>
     </row>
     <row r="10">
@@ -689,25 +689,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6325</v>
+        <v>14032</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9702387351778656</v>
+        <v>0.9145096921322691</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5363945304243087</v>
+        <v>0.5883485999179691</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09483003952569169</v>
+        <v>0.09781855758266818</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2437389749343307</v>
+        <v>0.2567270026807988</v>
       </c>
       <c r="G10" t="n">
-        <v>1.367805533596838</v>
+        <v>1.241168757126568</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8353014905650249</v>
+        <v>0.8283429809594004</v>
       </c>
     </row>
     <row r="11">
@@ -717,25 +717,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10532</v>
+        <v>14223</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7674306874287884</v>
+        <v>0.7577951205793433</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4811607087178721</v>
+        <v>0.4941309070727343</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1317071781238131</v>
+        <v>0.1256703930253814</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3259483442744441</v>
+        <v>0.315578321109832</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9513140903911887</v>
+        <v>0.847215777262181</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4446060324272965</v>
+        <v>0.4861502997662812</v>
       </c>
     </row>
     <row r="12">
@@ -745,25 +745,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2854</v>
+        <v>11122</v>
       </c>
       <c r="C12" t="n">
-        <v>1.076166783461808</v>
+        <v>0.9878016543787088</v>
       </c>
       <c r="D12" t="n">
-        <v>0.486587747159358</v>
+        <v>0.5689390810509394</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09069025928521372</v>
+        <v>0.1444901996043877</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2458467774678168</v>
+        <v>0.3807192658337801</v>
       </c>
       <c r="G12" t="n">
-        <v>2.203006306937631</v>
+        <v>1.898221542887969</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6821558694125696</v>
+        <v>0.7868617015082459</v>
       </c>
     </row>
     <row r="13">
@@ -773,25 +773,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6860</v>
+        <v>12754</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2449970845481049</v>
+        <v>0.2849788301709267</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3398650495759565</v>
+        <v>0.3856378362632406</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09591399416909621</v>
+        <v>0.1586733573780775</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2497800079617984</v>
+        <v>0.4006086830826951</v>
       </c>
       <c r="G13" t="n">
-        <v>1.258801749271137</v>
+        <v>1.052765406931159</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5965636335585103</v>
+        <v>0.6526859357830822</v>
       </c>
     </row>
     <row r="14">
@@ -801,25 +801,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7237</v>
+        <v>13677</v>
       </c>
       <c r="C14" t="n">
-        <v>1.221655382064391</v>
+        <v>1.206639613950428</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4034544670494482</v>
+        <v>0.480141632111098</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05435401409423794</v>
+        <v>0.06295459530598815</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1363077766676736</v>
+        <v>0.1640090972238768</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6412297913500069</v>
+        <v>0.6364948453608248</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3803547947387191</v>
+        <v>0.4100329710601752</v>
       </c>
     </row>
     <row r="15">
@@ -829,25 +829,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10167</v>
+        <v>14800</v>
       </c>
       <c r="C15" t="n">
-        <v>1.654733943149405</v>
+        <v>1.557407432432432</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4329955111331317</v>
+        <v>0.5027094789940337</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08649355758827579</v>
+        <v>0.09506216216216215</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2121552869036424</v>
+        <v>0.2441599161487151</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1341280613750369</v>
+        <v>0.1199027027027027</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1948369691483881</v>
+        <v>0.1984224661986737</v>
       </c>
     </row>
   </sheetData>
